--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,148 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>398400</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+        <v>8800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,8 +835,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -838,8 +866,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,57 +901,69 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>-500</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -925,8 +971,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +987,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>18000</v>
       </c>
       <c r="E17" s="3">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="F17" s="3">
-        <v>800</v>
+        <v>10200</v>
       </c>
       <c r="G17" s="3">
-        <v>1600</v>
+        <v>9900</v>
       </c>
       <c r="H17" s="3">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="I17" s="3">
-        <v>400</v>
+        <v>8000</v>
       </c>
       <c r="J17" s="3">
-        <v>200</v>
+        <v>3900</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3">
+        <v>200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,153 +1072,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-5500</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>303700</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+        <v>7900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G22" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>-200</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-51600</v>
       </c>
       <c r="E23" s="3">
-        <v>-900</v>
+        <v>-8800</v>
       </c>
       <c r="F23" s="3">
-        <v>1300</v>
+        <v>-11100</v>
       </c>
       <c r="G23" s="3">
-        <v>900</v>
+        <v>-10700</v>
       </c>
       <c r="H23" s="3">
-        <v>2800</v>
+        <v>19300</v>
       </c>
       <c r="I23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-51500</v>
       </c>
       <c r="E26" s="3">
-        <v>-900</v>
+        <v>-8900</v>
       </c>
       <c r="F26" s="3">
-        <v>1300</v>
+        <v>-8800</v>
       </c>
       <c r="G26" s="3">
-        <v>900</v>
+        <v>-8600</v>
       </c>
       <c r="H26" s="3">
-        <v>2800</v>
+        <v>17900</v>
       </c>
       <c r="I26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K26" s="3">
         <v>1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-51500</v>
       </c>
       <c r="E27" s="3">
-        <v>-900</v>
+        <v>-8900</v>
       </c>
       <c r="F27" s="3">
-        <v>1300</v>
+        <v>-8800</v>
       </c>
       <c r="G27" s="3">
-        <v>900</v>
+        <v>-8600</v>
       </c>
       <c r="H27" s="3">
-        <v>2800</v>
+        <v>17900</v>
       </c>
       <c r="I27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K27" s="3">
         <v>1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1488,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H32" s="3">
+        <v>26900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5500</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-51500</v>
       </c>
       <c r="E33" s="3">
-        <v>-900</v>
+        <v>-8900</v>
       </c>
       <c r="F33" s="3">
-        <v>1300</v>
+        <v>-8800</v>
       </c>
       <c r="G33" s="3">
-        <v>900</v>
+        <v>-8600</v>
       </c>
       <c r="H33" s="3">
-        <v>2800</v>
+        <v>17900</v>
       </c>
       <c r="I33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K33" s="3">
         <v>1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-51500</v>
       </c>
       <c r="E35" s="3">
-        <v>-900</v>
+        <v>-8900</v>
       </c>
       <c r="F35" s="3">
-        <v>1300</v>
+        <v>-8800</v>
       </c>
       <c r="G35" s="3">
-        <v>900</v>
+        <v>-8600</v>
       </c>
       <c r="H35" s="3">
-        <v>2800</v>
+        <v>17900</v>
       </c>
       <c r="I35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K35" s="3">
         <v>1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,13 +1702,15 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
+      <c r="D41" s="3">
+        <v>100</v>
       </c>
       <c r="E41" s="3">
         <v>100</v>
@@ -1545,225 +1719,273 @@
         <v>100</v>
       </c>
       <c r="G41" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>800</v>
-      </c>
-      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>12700</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>430800</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
+        <v>24900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>27400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>25500</v>
+      </c>
+      <c r="G43" s="3">
+        <v>24700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>16700</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
+      <c r="J43" s="3">
+        <v>13000</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1400</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>200</v>
+      </c>
+      <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>100</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
+      <c r="J44" s="3">
+        <v>100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>18800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>597400</v>
+        <v>32900</v>
       </c>
       <c r="E46" s="3">
-        <v>200</v>
+        <v>37700</v>
       </c>
       <c r="F46" s="3">
-        <v>300</v>
+        <v>35300</v>
       </c>
       <c r="G46" s="3">
-        <v>700</v>
+        <v>34300</v>
       </c>
       <c r="H46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I46" s="3">
+        <v>36400</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>6600</v>
       </c>
       <c r="E47" s="3">
-        <v>44700</v>
+        <v>7300</v>
       </c>
       <c r="F47" s="3">
-        <v>43700</v>
+        <v>6900</v>
       </c>
       <c r="G47" s="3">
-        <v>300000</v>
+        <v>6700</v>
       </c>
       <c r="H47" s="3">
-        <v>297600</v>
-      </c>
-      <c r="I47" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K47" s="3">
         <v>295200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>293800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18737600</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
+        <v>1009500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1078400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1043200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1012800</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1030000</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>865500</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1791,8 +2013,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2083,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>21500</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+        <v>60600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>67800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>66400</v>
+      </c>
+      <c r="G52" s="3">
+        <v>64400</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
+        <v>70000</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
+        <v>61900</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19473300</v>
+        <v>1109700</v>
       </c>
       <c r="E54" s="3">
-        <v>44800</v>
+        <v>1191300</v>
       </c>
       <c r="F54" s="3">
-        <v>43900</v>
+        <v>1151900</v>
       </c>
       <c r="G54" s="3">
-        <v>300700</v>
+        <v>1118300</v>
       </c>
       <c r="H54" s="3">
-        <v>298600</v>
-      </c>
-      <c r="I54" s="3">
+        <v>1146200</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="K54" s="3">
         <v>296400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>295200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2222,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>133000</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
+        <v>27100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>23600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>22900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>8700</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
+      <c r="J57" s="3">
+        <v>6400</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30000</v>
+        <v>415900</v>
       </c>
       <c r="E58" s="3">
-        <v>1300</v>
+        <v>139600</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
+        <v>130300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>126500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>215900</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>83400</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="3">
-        <v>3900</v>
+        <v>1800</v>
       </c>
       <c r="F59" s="3">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="G59" s="3">
-        <v>2600</v>
+        <v>1400</v>
       </c>
       <c r="H59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2627700</v>
+        <v>444700</v>
       </c>
       <c r="E60" s="3">
-        <v>5200</v>
+        <v>166200</v>
       </c>
       <c r="F60" s="3">
-        <v>3300</v>
+        <v>155400</v>
       </c>
       <c r="G60" s="3">
-        <v>2600</v>
+        <v>150900</v>
       </c>
       <c r="H60" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I60" s="3">
+        <v>226500</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4821300</v>
+        <v>72400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>315100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>290300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>281900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>151500</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13130300</v>
+        <v>3600</v>
       </c>
       <c r="E62" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="F62" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="G62" s="3">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="H62" s="3">
-        <v>15700</v>
-      </c>
-      <c r="I62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>17000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>17900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>741800</v>
       </c>
       <c r="E66" s="3">
-        <v>8700</v>
+        <v>728900</v>
       </c>
       <c r="F66" s="3">
-        <v>6900</v>
+        <v>688500</v>
       </c>
       <c r="G66" s="3">
-        <v>6400</v>
+        <v>668400</v>
       </c>
       <c r="H66" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I66" s="3">
+        <v>632200</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="K66" s="3">
         <v>17600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1181000</v>
+        <v>-125400</v>
       </c>
       <c r="E72" s="3">
-        <v>-20400</v>
+        <v>-81500</v>
       </c>
       <c r="F72" s="3">
-        <v>-18400</v>
+        <v>-69900</v>
       </c>
       <c r="G72" s="3">
-        <v>-17500</v>
+        <v>-67800</v>
       </c>
       <c r="H72" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="I72" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-16400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-16800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7834200</v>
+        <v>367900</v>
       </c>
       <c r="E76" s="3">
-        <v>36100</v>
+        <v>462400</v>
       </c>
       <c r="F76" s="3">
-        <v>37100</v>
+        <v>463400</v>
       </c>
       <c r="G76" s="3">
-        <v>294300</v>
+        <v>449900</v>
       </c>
       <c r="H76" s="3">
-        <v>281600</v>
+        <v>514000</v>
       </c>
       <c r="I76" s="3">
+        <v>465600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="K76" s="3">
         <v>278800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>276900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-51500</v>
       </c>
       <c r="E81" s="3">
-        <v>-900</v>
+        <v>-8900</v>
       </c>
       <c r="F81" s="3">
-        <v>1300</v>
+        <v>-8800</v>
       </c>
       <c r="G81" s="3">
-        <v>900</v>
+        <v>-8600</v>
       </c>
       <c r="H81" s="3">
-        <v>2800</v>
+        <v>17900</v>
       </c>
       <c r="I81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K81" s="3">
         <v>1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,16 +3027,18 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -2654,14 +3052,20 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>166200</v>
+        <v>1000</v>
       </c>
       <c r="E89" s="3">
-        <v>-400</v>
+        <v>-5400</v>
       </c>
       <c r="F89" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="G89" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="H89" s="3">
-        <v>-200</v>
+        <v>13900</v>
       </c>
       <c r="I89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3287,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-16700</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-22300</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-21600</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-25900</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-19300</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3388,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-31200</v>
       </c>
       <c r="E94" s="3">
-        <v>-400</v>
+        <v>-18200</v>
       </c>
       <c r="F94" s="3">
-        <v>258100</v>
+        <v>-24900</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-24100</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-27800</v>
       </c>
       <c r="I94" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3442,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3578,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1695400</v>
+        <v>28500</v>
       </c>
       <c r="E100" s="3">
-        <v>800</v>
+        <v>24200</v>
       </c>
       <c r="F100" s="3">
-        <v>-258100</v>
+        <v>19200</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>18700</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-93700</v>
+        <v>-1600</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,45 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
@@ -709,30 +710,33 @@
         <v>44926</v>
       </c>
       <c r="K7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E8" s="3">
         <v>8800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6500</v>
       </c>
-      <c r="F8" s="3">
-        <v>5300</v>
-      </c>
       <c r="G8" s="3">
-        <v>5100</v>
+        <v>3800</v>
       </c>
       <c r="H8" s="3">
         <v>3700</v>
@@ -743,8 +747,8 @@
       <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
+      <c r="K8" s="3">
+        <v>100</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
@@ -752,22 +756,25 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5500</v>
       </c>
-      <c r="F9" s="3">
-        <v>1500</v>
-      </c>
       <c r="G9" s="3">
-        <v>1400</v>
+        <v>8200</v>
       </c>
       <c r="H9" s="3">
         <v>-2500</v>
@@ -778,8 +785,8 @@
       <c r="J9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>100</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -787,22 +794,25 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
-        <v>3800</v>
-      </c>
       <c r="G10" s="3">
-        <v>3700</v>
+        <v>-4500</v>
       </c>
       <c r="H10" s="3">
         <v>6300</v>
@@ -813,8 +823,8 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
@@ -822,8 +832,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +850,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +886,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +924,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -918,11 +938,11 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>2800</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>2700</v>
+        <v>500</v>
       </c>
       <c r="H14" s="3">
         <v>-500</v>
@@ -934,7 +954,7 @@
         <v>-7000</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -942,22 +962,25 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="3">
         <v>4500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
-        <v>3600</v>
-      </c>
       <c r="G15" s="3">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="H15" s="3">
         <v>-1000</v>
@@ -977,8 +1000,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,22 +1015,23 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E17" s="3">
         <v>18000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16000</v>
       </c>
-      <c r="F17" s="3">
-        <v>10200</v>
-      </c>
       <c r="G17" s="3">
-        <v>9900</v>
+        <v>10900</v>
       </c>
       <c r="H17" s="3">
         <v>6000</v>
@@ -1016,30 +1043,33 @@
         <v>3900</v>
       </c>
       <c r="K17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-4900</v>
-      </c>
       <c r="G18" s="3">
-        <v>-4800</v>
+        <v>-7100</v>
       </c>
       <c r="H18" s="3">
         <v>-2200</v>
@@ -1050,8 +1080,8 @@
       <c r="J18" s="3">
         <v>-3800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
+      <c r="K18" s="3">
+        <v>-3800</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
@@ -1059,8 +1089,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,22 +1107,23 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E20" s="3">
         <v>34700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="F20" s="3">
-        <v>-2900</v>
-      </c>
       <c r="G20" s="3">
-        <v>-2800</v>
+        <v>4300</v>
       </c>
       <c r="H20" s="3">
         <v>-26900</v>
@@ -1100,8 +1134,8 @@
       <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
+      <c r="K20" s="3">
+        <v>-5500</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1109,22 +1143,25 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-39400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
-        <v>1500</v>
-      </c>
       <c r="G21" s="3">
-        <v>1500</v>
+        <v>-6600</v>
       </c>
       <c r="H21" s="3">
         <v>23700</v>
@@ -1135,8 +1172,8 @@
       <c r="J21" s="3">
         <v>1700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
+      <c r="K21" s="3">
+        <v>1700</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
@@ -1144,22 +1181,25 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5700</v>
       </c>
-      <c r="F22" s="3">
-        <v>6400</v>
-      </c>
       <c r="G22" s="3">
-        <v>6300</v>
+        <v>3400</v>
       </c>
       <c r="H22" s="3">
         <v>5900</v>
@@ -1170,8 +1210,8 @@
       <c r="J22" s="3">
         <v>-200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>-200</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
@@ -1179,22 +1219,25 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-51600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-11100</v>
-      </c>
       <c r="G23" s="3">
-        <v>-10700</v>
+        <v>-15200</v>
       </c>
       <c r="H23" s="3">
         <v>19300</v>
@@ -1206,30 +1249,33 @@
         <v>8900</v>
       </c>
       <c r="K23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="L23" s="3">
         <v>1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>-2200</v>
-      </c>
       <c r="G24" s="3">
-        <v>-2200</v>
+        <v>-3600</v>
       </c>
       <c r="H24" s="3">
         <v>1400</v>
@@ -1241,7 +1287,7 @@
         <v>4700</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1249,8 +1295,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,22 +1333,25 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G26" s="3">
-        <v>-8600</v>
+        <v>-11500</v>
       </c>
       <c r="H26" s="3">
         <v>17900</v>
@@ -1311,30 +1363,33 @@
         <v>4200</v>
       </c>
       <c r="K26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G27" s="3">
-        <v>-8600</v>
+        <v>-11500</v>
       </c>
       <c r="H27" s="3">
         <v>17900</v>
@@ -1346,16 +1401,19 @@
         <v>4200</v>
       </c>
       <c r="K27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1447,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1485,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1523,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,22 +1561,25 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-34700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="F32" s="3">
-        <v>2900</v>
-      </c>
       <c r="G32" s="3">
-        <v>2800</v>
+        <v>-4300</v>
       </c>
       <c r="H32" s="3">
         <v>26900</v>
@@ -1520,8 +1590,8 @@
       <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
+      <c r="K32" s="3">
+        <v>5500</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
@@ -1529,22 +1599,25 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-51500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G33" s="3">
-        <v>-8600</v>
+        <v>-11500</v>
       </c>
       <c r="H33" s="3">
         <v>17900</v>
@@ -1556,16 +1629,19 @@
         <v>4200</v>
       </c>
       <c r="K33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L33" s="3">
         <v>1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,22 +1675,25 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-51500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G35" s="3">
-        <v>-8600</v>
+        <v>-11500</v>
       </c>
       <c r="H35" s="3">
         <v>17900</v>
@@ -1626,32 +1705,35 @@
         <v>4200</v>
       </c>
       <c r="K35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L35" s="3">
         <v>1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
@@ -1666,16 +1748,19 @@
         <v>44926</v>
       </c>
       <c r="K38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1774,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,8 +1790,9 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1718,8 +1805,8 @@
       <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>100</v>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H41" s="3">
         <v>0</v>
@@ -1731,30 +1818,33 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4900</v>
       </c>
-      <c r="F42" s="3">
-        <v>4700</v>
-      </c>
       <c r="G42" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>12700</v>
@@ -1766,7 +1856,7 @@
         <v>11000</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1774,22 +1864,25 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E43" s="3">
         <v>24900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27400</v>
       </c>
-      <c r="F43" s="3">
-        <v>25500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>24700</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>16700</v>
@@ -1800,8 +1893,8 @@
       <c r="J43" s="3">
         <v>13000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>13000</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -1809,8 +1902,11 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1818,13 +1914,13 @@
         <v>500</v>
       </c>
       <c r="E44" s="3">
+        <v>500</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
-        <v>100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>100</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -1835,8 +1931,8 @@
       <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
+      <c r="K44" s="3">
+        <v>100</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
@@ -1844,8 +1940,11 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1870,31 +1969,34 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E46" s="3">
         <v>32900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37700</v>
       </c>
-      <c r="F46" s="3">
-        <v>35300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>34300</v>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H46" s="3">
         <v>36400</v>
@@ -1906,30 +2008,33 @@
         <v>26600</v>
       </c>
       <c r="K46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="L46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>6600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7300</v>
       </c>
-      <c r="F47" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>6700</v>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>9800</v>
@@ -1941,30 +2046,33 @@
         <v>9900</v>
       </c>
       <c r="K47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="L47" s="3">
         <v>295200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>293800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>946900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1009500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1078400</v>
       </c>
-      <c r="F48" s="3">
-        <v>1043200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1012800</v>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H48" s="3">
         <v>1030000</v>
@@ -1975,8 +2083,8 @@
       <c r="J48" s="3">
         <v>865500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
+      <c r="K48" s="3">
+        <v>865500</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
@@ -1984,8 +2092,11 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1998,8 +2109,8 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -2019,8 +2130,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2168,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,22 +2206,25 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E52" s="3">
         <v>60600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67800</v>
       </c>
-      <c r="F52" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>64400</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
         <v>70000</v>
@@ -2116,16 +2236,19 @@
         <v>61900</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,22 +2282,25 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1061800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1109700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1191300</v>
       </c>
-      <c r="F54" s="3">
-        <v>1151900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1118300</v>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H54" s="3">
         <v>1146200</v>
@@ -2186,16 +2312,19 @@
         <v>963900</v>
       </c>
       <c r="K54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="L54" s="3">
         <v>296400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>295200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2338,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,22 +2354,23 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E57" s="3">
         <v>27100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24700</v>
       </c>
-      <c r="F57" s="3">
-        <v>23600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>22900</v>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H57" s="3">
         <v>8700</v>
@@ -2250,8 +2381,8 @@
       <c r="J57" s="3">
         <v>6400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
+      <c r="K57" s="3">
+        <v>6400</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
@@ -2259,22 +2390,25 @@
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E58" s="3">
         <v>415900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>139600</v>
       </c>
-      <c r="F58" s="3">
-        <v>130300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>126500</v>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H58" s="3">
         <v>215900</v>
@@ -2286,7 +2420,7 @@
         <v>198100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2294,22 +2428,25 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1400</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
         <v>1800</v>
@@ -2321,30 +2458,33 @@
         <v>4000</v>
       </c>
       <c r="K59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E60" s="3">
         <v>444700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>166200</v>
       </c>
-      <c r="F60" s="3">
-        <v>155400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>150900</v>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
         <v>226500</v>
@@ -2356,30 +2496,33 @@
         <v>208600</v>
       </c>
       <c r="K60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>456300</v>
+      </c>
+      <c r="E61" s="3">
         <v>72400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>315100</v>
       </c>
-      <c r="F61" s="3">
-        <v>290300</v>
-      </c>
       <c r="G61" s="3">
-        <v>281900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>151500</v>
@@ -2391,7 +2534,7 @@
         <v>101200</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2399,22 +2542,25 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E62" s="3">
         <v>3600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3700</v>
       </c>
       <c r="F62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3">
-        <v>3600</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>2000</v>
@@ -2425,17 +2571,20 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>17000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2618,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2656,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,22 +2694,25 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>762000</v>
+      </c>
+      <c r="E66" s="3">
         <v>741800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>728900</v>
       </c>
-      <c r="F66" s="3">
-        <v>688500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>668400</v>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H66" s="3">
         <v>632200</v>
@@ -2566,16 +2724,19 @@
         <v>533300</v>
       </c>
       <c r="K66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="L66" s="3">
         <v>17600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2750,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2786,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2824,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2862,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,22 +2900,25 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-160400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-125400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-81500</v>
       </c>
-      <c r="F72" s="3">
-        <v>-69900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-67800</v>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H72" s="3">
         <v>-48100</v>
@@ -2756,16 +2930,19 @@
         <v>-63500</v>
       </c>
       <c r="K72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="L72" s="3">
         <v>-16400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-16800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2976,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3014,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,22 +3052,25 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>299900</v>
+      </c>
+      <c r="E76" s="3">
         <v>367900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>462400</v>
       </c>
-      <c r="F76" s="3">
-        <v>463400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>449900</v>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H76" s="3">
         <v>514000</v>
@@ -2896,16 +3082,19 @@
         <v>430600</v>
       </c>
       <c r="K76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="L76" s="3">
         <v>278800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>276900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,24 +3128,27 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
@@ -2971,30 +3163,33 @@
         <v>44926</v>
       </c>
       <c r="K80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-51500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-8800</v>
-      </c>
       <c r="G81" s="3">
-        <v>-8600</v>
+        <v>-11500</v>
       </c>
       <c r="H81" s="3">
         <v>17900</v>
@@ -3006,16 +3201,19 @@
         <v>4200</v>
       </c>
       <c r="K81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L81" s="3">
         <v>1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,8 +3227,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3055,8 +3254,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -3064,8 +3263,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3301,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3339,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3377,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3415,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,22 +3453,25 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5400</v>
       </c>
-      <c r="F89" s="3">
-        <v>300</v>
-      </c>
       <c r="G89" s="3">
-        <v>300</v>
+        <v>-3700</v>
       </c>
       <c r="H89" s="3">
         <v>13900</v>
@@ -3266,16 +3483,19 @@
         <v>-10900</v>
       </c>
       <c r="K89" s="3">
-        <v>-100</v>
+        <v>-10900</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
       </c>
       <c r="M89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,22 +3509,23 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16700</v>
       </c>
-      <c r="F91" s="3">
-        <v>-22300</v>
-      </c>
       <c r="G91" s="3">
-        <v>-21600</v>
+        <v>-31200</v>
       </c>
       <c r="H91" s="3">
         <v>-25900</v>
@@ -3316,7 +3537,7 @@
         <v>-21100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3324,8 +3545,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3583,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,22 +3621,25 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18200</v>
       </c>
-      <c r="F94" s="3">
-        <v>-24900</v>
-      </c>
       <c r="G94" s="3">
-        <v>-24100</v>
+        <v>-33800</v>
       </c>
       <c r="H94" s="3">
         <v>-27800</v>
@@ -3421,16 +3651,19 @@
         <v>-18900</v>
       </c>
       <c r="K94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3677,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3470,8 +3704,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3479,8 +3713,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3751,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3789,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,22 +3827,25 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E100" s="3">
         <v>28500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24200</v>
       </c>
-      <c r="F100" s="3">
-        <v>19200</v>
-      </c>
       <c r="G100" s="3">
-        <v>18700</v>
+        <v>39400</v>
       </c>
       <c r="H100" s="3">
         <v>19100</v>
@@ -3611,16 +3857,19 @@
         <v>28400</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3645,8 +3894,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3654,22 +3903,25 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
-        <v>-5300</v>
-      </c>
       <c r="G102" s="3">
-        <v>-5100</v>
+        <v>1900</v>
       </c>
       <c r="H102" s="3">
         <v>5200</v>
@@ -3681,12 +3933,15 @@
         <v>-1300</v>
       </c>
       <c r="K102" s="3">
-        <v>-100</v>
+        <v>-1300</v>
       </c>
       <c r="L102" s="3">
         <v>-100</v>
       </c>
       <c r="M102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,102 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
       </c>
       <c r="L7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E8" s="3">
         <v>8500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3700</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
+      <c r="L8" s="3">
+        <v>100</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
@@ -759,37 +761,40 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E9" s="3">
         <v>5900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5500</v>
       </c>
-      <c r="G9" s="3">
-        <v>8200</v>
-      </c>
       <c r="H9" s="3">
-        <v>-2500</v>
+        <v>3800</v>
       </c>
       <c r="I9" s="3">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>1900</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>100</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -797,37 +802,40 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
-        <v>-4500</v>
-      </c>
       <c r="H10" s="3">
-        <v>6300</v>
+        <v>2900</v>
       </c>
       <c r="I10" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -835,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,13 +942,16 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-11500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -941,23 +959,23 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-7000</v>
       </c>
       <c r="K14" s="3">
         <v>-7000</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -965,32 +983,35 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E15" s="3">
         <v>4400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I15" s="3">
         <v>4800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>-1000</v>
       </c>
-      <c r="I15" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1003,8 +1024,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,75 +1040,79 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E17" s="3">
         <v>17300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I17" s="3">
         <v>10900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3900</v>
       </c>
       <c r="K17" s="3">
         <v>3900</v>
       </c>
       <c r="L17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-3800</v>
       </c>
       <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
+      <c r="L18" s="3">
+        <v>-3800</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
@@ -1092,8 +1120,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,37 +1139,38 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E20" s="3">
         <v>30300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="I20" s="3">
         <v>4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-26900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-5500</v>
       </c>
       <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
+      <c r="L20" s="3">
+        <v>-5500</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
@@ -1146,37 +1178,40 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-34700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-39400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>23700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>7700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1700</v>
       </c>
       <c r="K21" s="3">
         <v>1700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
+      <c r="L21" s="3">
+        <v>1700</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
@@ -1184,37 +1219,40 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E22" s="3">
         <v>9800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I22" s="3">
         <v>3400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>-200</v>
       </c>
       <c r="K22" s="3">
         <v>-200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="L22" s="3">
+        <v>-200</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1222,75 +1260,81 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-51600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-15200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>19300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>8900</v>
       </c>
       <c r="K23" s="3">
         <v>8900</v>
       </c>
       <c r="L23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I24" s="3">
         <v>-3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>4700</v>
       </c>
       <c r="K24" s="3">
         <v>4700</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1298,8 +1342,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-43400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-51500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-11500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>17900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>4200</v>
       </c>
       <c r="K26" s="3">
         <v>4200</v>
       </c>
       <c r="L26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-43400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-51500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-11500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>17900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>4200</v>
       </c>
       <c r="K27" s="3">
         <v>4200</v>
       </c>
       <c r="L27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,37 +1629,40 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>26900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>11600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5500</v>
       </c>
       <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
+      <c r="L32" s="3">
+        <v>5500</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
@@ -1602,46 +1670,52 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-43400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-51500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-11500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>17900</v>
-      </c>
-      <c r="I33" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>4200</v>
       </c>
       <c r="K33" s="3">
         <v>4200</v>
       </c>
       <c r="L33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M33" s="3">
         <v>1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-43400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-51500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-11500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>17900</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>4200</v>
       </c>
       <c r="K35" s="3">
         <v>4200</v>
       </c>
       <c r="L35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M35" s="3">
         <v>1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
       </c>
       <c r="L38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,8 +1875,9 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1805,11 +1890,11 @@
       <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
+      <c r="G41" s="3">
+        <v>100</v>
       </c>
       <c r="H41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
@@ -1821,45 +1906,48 @@
         <v>0</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E42" s="3">
         <v>15000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4900</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>12700</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>11000</v>
       </c>
       <c r="K42" s="3">
         <v>11000</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1867,37 +1955,40 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E43" s="3">
         <v>22400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3">
+        <v>25500</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>16700</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
-        <v>13000</v>
       </c>
       <c r="K43" s="3">
         <v>13000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
+      <c r="L43" s="3">
+        <v>13000</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
@@ -1905,37 +1996,40 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E44" s="3">
         <v>500</v>
       </c>
       <c r="F44" s="3">
+        <v>500</v>
+      </c>
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
+      <c r="L44" s="3">
+        <v>100</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
@@ -1943,8 +2037,11 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1972,122 +2069,131 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E46" s="3">
         <v>58500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37700</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H46" s="3">
+        <v>35300</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>36400</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
-        <v>26600</v>
       </c>
       <c r="K46" s="3">
         <v>26600</v>
       </c>
       <c r="L46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="M46" s="3">
         <v>1200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>6600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7300</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H47" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>9800</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
-        <v>9900</v>
       </c>
       <c r="K47" s="3">
         <v>9900</v>
       </c>
       <c r="L47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="M47" s="3">
         <v>295200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>293800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>968200</v>
+      </c>
+      <c r="E48" s="3">
         <v>946900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1009500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1078400</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3">
+        <v>1043200</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>1030000</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
-        <v>865500</v>
       </c>
       <c r="K48" s="3">
         <v>865500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
+      <c r="L48" s="3">
+        <v>865500</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
@@ -2095,8 +2201,11 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2109,14 +2218,14 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
+      <c r="G49" s="3">
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -2133,8 +2242,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2324,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E52" s="3">
         <v>56400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67800</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3">
+        <v>66400</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>70000</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
-        <v>61900</v>
       </c>
       <c r="K52" s="3">
         <v>61900</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2406,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1104400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1061800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1109700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1191300</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H54" s="3">
+        <v>1151900</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>1146200</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
-        <v>963900</v>
       </c>
       <c r="K54" s="3">
         <v>963900</v>
       </c>
       <c r="L54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="M54" s="3">
         <v>296400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>295200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,37 +2483,38 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E57" s="3">
         <v>30200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24700</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3">
+        <v>23600</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>8700</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
-        <v>6400</v>
       </c>
       <c r="K57" s="3">
         <v>6400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
+      <c r="L57" s="3">
+        <v>6400</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
@@ -2393,37 +2522,40 @@
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>175100</v>
+      </c>
+      <c r="E58" s="3">
         <v>67200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>415900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>139600</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3">
+        <v>130300</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
         <v>215900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>198100</v>
       </c>
       <c r="K58" s="3">
         <v>198100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2431,113 +2563,122 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>1800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
-        <v>4000</v>
       </c>
       <c r="K59" s="3">
         <v>4000</v>
       </c>
       <c r="L59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E60" s="3">
         <v>99300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>444700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>166200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H60" s="3">
+        <v>155400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>226500</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
-        <v>208600</v>
       </c>
       <c r="K60" s="3">
         <v>208600</v>
       </c>
       <c r="L60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E61" s="3">
         <v>456300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>72400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>315100</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>290300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>151500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>101200</v>
       </c>
       <c r="K61" s="3">
         <v>101200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -2545,46 +2686,52 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>4300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>17000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>17900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +2850,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800200</v>
+      </c>
+      <c r="E66" s="3">
         <v>762000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>741800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>728900</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H66" s="3">
+        <v>688500</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>632200</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
-        <v>533300</v>
       </c>
       <c r="K66" s="3">
         <v>533300</v>
       </c>
       <c r="L66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="M66" s="3">
         <v>17600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3072,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-178300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-160400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-125400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-81500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3">
+        <v>-69900</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>-48100</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-63500</v>
       </c>
       <c r="K72" s="3">
         <v>-63500</v>
       </c>
       <c r="L72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="M72" s="3">
         <v>-16400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3236,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>304100</v>
+      </c>
+      <c r="E76" s="3">
         <v>299900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>367900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>462400</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H76" s="3">
+        <v>463400</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>514000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>465600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>430600</v>
       </c>
       <c r="K76" s="3">
         <v>430600</v>
       </c>
       <c r="L76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="M76" s="3">
         <v>278800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>276900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
       </c>
       <c r="L80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-43400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-51500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-11500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>17900</v>
-      </c>
-      <c r="I81" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>4200</v>
       </c>
       <c r="K81" s="3">
         <v>4200</v>
       </c>
       <c r="L81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M81" s="3">
         <v>1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,37 +3424,38 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F83" s="3">
         <v>-1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1800</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3266,8 +3463,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>13900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-10900</v>
       </c>
       <c r="K89" s="3">
         <v>-10900</v>
       </c>
       <c r="L89" s="3">
-        <v>-100</v>
+        <v>-10900</v>
       </c>
       <c r="M89" s="3">
         <v>-100</v>
       </c>
       <c r="N89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,37 +3728,38 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-31200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-25900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-19300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-21100</v>
       </c>
       <c r="K91" s="3">
         <v>-21100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3548,8 +3767,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-33800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-27800</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-18900</v>
       </c>
       <c r="K94" s="3">
         <v>-18900</v>
       </c>
       <c r="L94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3707,8 +3939,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3716,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,46 +4071,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E100" s="3">
         <v>27300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>28500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I100" s="3">
         <v>39400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>19100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>25500</v>
-      </c>
-      <c r="J100" s="3">
-        <v>28400</v>
       </c>
       <c r="K100" s="3">
         <v>28400</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3897,8 +4144,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3906,42 +4153,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E102" s="3">
         <v>28300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>5200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1300</v>
       </c>
       <c r="K102" s="3">
         <v>-1300</v>
       </c>
       <c r="L102" s="3">
-        <v>-100</v>
+        <v>-1300</v>
       </c>
       <c r="M102" s="3">
         <v>-100</v>
       </c>
       <c r="N102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,107 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
-      </c>
-      <c r="K7" s="2">
-        <v>44926</v>
       </c>
       <c r="L7" s="2">
         <v>44926</v>
       </c>
       <c r="M7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E8" s="3">
         <v>14200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8500</v>
       </c>
-      <c r="F8" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
         <v>6500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
+      <c r="M8" s="3">
+        <v>100</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
@@ -764,40 +768,43 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>7500</v>
+        <v>7300</v>
       </c>
       <c r="E9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F9" s="3">
         <v>5900</v>
       </c>
-      <c r="F9" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3">
         <v>5500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3800</v>
       </c>
       <c r="I9" s="3">
         <v>3800</v>
       </c>
       <c r="J9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K9" s="3">
         <v>1900</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>100</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -805,40 +812,43 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>6700</v>
+        <v>8400</v>
       </c>
       <c r="E10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2600</v>
       </c>
-      <c r="F10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -846,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,40 +962,43 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>-11500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>5000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-7000</v>
       </c>
       <c r="L14" s="3">
         <v>-7000</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -986,35 +1006,38 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="E15" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
-        <v>4500</v>
-      </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>2700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-1000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,81 +1067,85 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20400</v>
+        <v>18700</v>
       </c>
       <c r="E17" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F17" s="3">
         <v>17300</v>
       </c>
-      <c r="F17" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3">
         <v>16000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3900</v>
       </c>
       <c r="L17" s="3">
         <v>3900</v>
       </c>
       <c r="M17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6200</v>
+        <v>-3000</v>
       </c>
       <c r="E18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8800</v>
       </c>
-      <c r="F18" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
         <v>-9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-3800</v>
       </c>
       <c r="L18" s="3">
         <v>-3800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
+      <c r="M18" s="3">
+        <v>-3800</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
@@ -1123,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,40 +1173,41 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12700</v>
+        <v>-2400</v>
       </c>
       <c r="E20" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F20" s="3">
         <v>30300</v>
       </c>
-      <c r="F20" s="3">
-        <v>34700</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
         <v>-6200</v>
       </c>
-      <c r="H20" s="3">
-        <v>-10200</v>
-      </c>
       <c r="I20" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="J20" s="3">
         <v>4300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-5500</v>
       </c>
       <c r="L20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
+      <c r="M20" s="3">
+        <v>-5500</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
@@ -1181,40 +1215,43 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-14800</v>
+        <v>3200</v>
       </c>
       <c r="E21" s="3">
+        <v>-59600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-34700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-39400</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
-        <v>9900</v>
-      </c>
       <c r="I21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-6600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1700</v>
       </c>
       <c r="L21" s="3">
         <v>1700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
+      <c r="M21" s="3">
+        <v>1700</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
@@ -1222,40 +1259,43 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E22" s="3">
         <v>17600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9800</v>
       </c>
-      <c r="F22" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>5700</v>
       </c>
-      <c r="H22" s="3">
-        <v>9400</v>
-      </c>
       <c r="I22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J22" s="3">
         <v>3400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>-200</v>
       </c>
       <c r="L22" s="3">
         <v>-200</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>-200</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1263,81 +1303,87 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-24700</v>
+        <v>-17600</v>
       </c>
       <c r="E23" s="3">
+        <v>-70600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-47800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-51600</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>8900</v>
       </c>
       <c r="L23" s="3">
         <v>8900</v>
       </c>
       <c r="M23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2800</v>
+        <v>-2000</v>
       </c>
       <c r="E24" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-4400</v>
       </c>
-      <c r="F24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>4700</v>
       </c>
       <c r="L24" s="3">
         <v>4700</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1345,8 +1391,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1435,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-27600</v>
+        <v>-15500</v>
       </c>
       <c r="E26" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-43400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>4200</v>
       </c>
       <c r="L26" s="3">
         <v>4200</v>
       </c>
       <c r="M26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-27600</v>
+        <v>-15500</v>
       </c>
       <c r="E27" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-43400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>4200</v>
       </c>
       <c r="L27" s="3">
         <v>4200</v>
       </c>
       <c r="M27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,40 +1699,43 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12700</v>
+        <v>2400</v>
       </c>
       <c r="E32" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-30300</v>
       </c>
-      <c r="F32" s="3">
-        <v>-34700</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>6200</v>
       </c>
-      <c r="H32" s="3">
-        <v>10200</v>
-      </c>
       <c r="I32" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>5500</v>
       </c>
       <c r="L32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
+      <c r="M32" s="3">
+        <v>5500</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
@@ -1673,49 +1743,55 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-27600</v>
+        <v>-15500</v>
       </c>
       <c r="E33" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-43400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>4200</v>
       </c>
       <c r="L33" s="3">
         <v>4200</v>
       </c>
       <c r="M33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N33" s="3">
         <v>1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1831,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-27600</v>
+        <v>-15500</v>
       </c>
       <c r="E35" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-43400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>4200</v>
       </c>
       <c r="L35" s="3">
         <v>4200</v>
       </c>
       <c r="M35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N35" s="3">
         <v>1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
-      </c>
-      <c r="K38" s="2">
-        <v>44926</v>
       </c>
       <c r="L38" s="2">
         <v>44926</v>
       </c>
       <c r="M38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,8 +1962,9 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1890,17 +1977,17 @@
       <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>100</v>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+      <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -1909,48 +1996,51 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E42" s="3">
         <v>28100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15000</v>
       </c>
-      <c r="F42" s="3">
-        <v>4500</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>4900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>12700</v>
-      </c>
-      <c r="K42" s="3">
-        <v>11000</v>
       </c>
       <c r="L42" s="3">
         <v>11000</v>
       </c>
       <c r="M42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1958,40 +2048,43 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>22100</v>
+        <v>25100</v>
       </c>
       <c r="E43" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F43" s="3">
         <v>22400</v>
       </c>
-      <c r="F43" s="3">
-        <v>24900</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>27400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>16700</v>
-      </c>
-      <c r="K43" s="3">
-        <v>13000</v>
       </c>
       <c r="L43" s="3">
         <v>13000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
+      <c r="M43" s="3">
+        <v>13000</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
@@ -1999,8 +2092,11 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2008,31 +2104,31 @@
         <v>600</v>
       </c>
       <c r="E44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
+      <c r="M44" s="3">
+        <v>100</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
@@ -2040,8 +2136,11 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2072,58 +2171,64 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>70900</v>
+        <v>49500</v>
       </c>
       <c r="E46" s="3">
+        <v>71600</v>
+      </c>
+      <c r="F46" s="3">
         <v>58500</v>
       </c>
-      <c r="F46" s="3">
-        <v>32900</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>37700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>36400</v>
-      </c>
-      <c r="K46" s="3">
-        <v>26600</v>
       </c>
       <c r="L46" s="3">
         <v>26600</v>
       </c>
       <c r="M46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="N46" s="3">
         <v>1200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2133,70 +2238,73 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
-        <v>6600</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>7300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>9800</v>
-      </c>
-      <c r="K47" s="3">
-        <v>9900</v>
       </c>
       <c r="L47" s="3">
         <v>9900</v>
       </c>
       <c r="M47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="N47" s="3">
         <v>295200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>293800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>968200</v>
+        <v>933300</v>
       </c>
       <c r="E48" s="3">
+        <v>912600</v>
+      </c>
+      <c r="F48" s="3">
         <v>946900</v>
       </c>
-      <c r="F48" s="3">
-        <v>1009500</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>1078400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1043200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>1030000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>865500</v>
       </c>
       <c r="L48" s="3">
         <v>865500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
+      <c r="M48" s="3">
+        <v>865500</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
@@ -2204,8 +2312,11 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2218,17 +2329,17 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,49 +2444,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>65200</v>
+        <v>66500</v>
       </c>
       <c r="E52" s="3">
+        <v>65400</v>
+      </c>
+      <c r="F52" s="3">
         <v>56400</v>
       </c>
-      <c r="F52" s="3">
-        <v>60600</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>67800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>66400</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>70000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>61900</v>
       </c>
       <c r="L52" s="3">
         <v>61900</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2532,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1104400</v>
+        <v>1049400</v>
       </c>
       <c r="E54" s="3">
+        <v>1049600</v>
+      </c>
+      <c r="F54" s="3">
         <v>1061800</v>
       </c>
-      <c r="F54" s="3">
-        <v>1109700</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>1191300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1151900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>1146200</v>
-      </c>
-      <c r="K54" s="3">
-        <v>963900</v>
       </c>
       <c r="L54" s="3">
         <v>963900</v>
       </c>
       <c r="M54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="N54" s="3">
         <v>296400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>295200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,40 +2614,41 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>25300</v>
+        <v>28100</v>
       </c>
       <c r="E57" s="3">
         <v>30200</v>
       </c>
       <c r="F57" s="3">
-        <v>27100</v>
-      </c>
-      <c r="G57" s="3">
+        <v>30200</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>24700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23600</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>8700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>6400</v>
       </c>
       <c r="L57" s="3">
         <v>6400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
+      <c r="M57" s="3">
+        <v>6400</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
@@ -2525,40 +2656,43 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>170700</v>
+      </c>
+      <c r="E58" s="3">
         <v>175100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67200</v>
       </c>
-      <c r="F58" s="3">
-        <v>415900</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>139600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>130300</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
         <v>215900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>198100</v>
       </c>
       <c r="L58" s="3">
         <v>198100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2566,122 +2700,131 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>1800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4000</v>
       </c>
       <c r="L59" s="3">
         <v>4000</v>
       </c>
       <c r="M59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>202100</v>
+        <v>200400</v>
       </c>
       <c r="E60" s="3">
+        <v>209500</v>
+      </c>
+      <c r="F60" s="3">
         <v>99300</v>
       </c>
-      <c r="F60" s="3">
-        <v>444700</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>166200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>155400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>226500</v>
-      </c>
-      <c r="K60" s="3">
-        <v>208600</v>
       </c>
       <c r="L60" s="3">
         <v>208600</v>
       </c>
       <c r="M60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>391500</v>
+      </c>
+      <c r="E61" s="3">
         <v>380400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>456300</v>
       </c>
-      <c r="F61" s="3">
-        <v>72400</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>315100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>290300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>151500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>101200</v>
       </c>
       <c r="L61" s="3">
         <v>101200</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -2689,8 +2832,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2698,40 +2844,43 @@
         <v>4100</v>
       </c>
       <c r="E62" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F62" s="3">
         <v>4300</v>
       </c>
-      <c r="F62" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3700</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="I62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>17000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3008,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800200</v>
+        <v>800000</v>
       </c>
       <c r="E66" s="3">
+        <v>799800</v>
+      </c>
+      <c r="F66" s="3">
         <v>762000</v>
       </c>
-      <c r="F66" s="3">
-        <v>741800</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>728900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>688500</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>632200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>533300</v>
       </c>
       <c r="L66" s="3">
         <v>533300</v>
       </c>
       <c r="M66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="N66" s="3">
         <v>17600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3246,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-178300</v>
+        <v>-203100</v>
       </c>
       <c r="E72" s="3">
+        <v>-228900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-160400</v>
       </c>
-      <c r="F72" s="3">
-        <v>-125400</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-81500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-69900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-48100</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-63500</v>
       </c>
       <c r="L72" s="3">
         <v>-63500</v>
       </c>
       <c r="M72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="N72" s="3">
         <v>-16400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-16800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3422,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>304100</v>
+        <v>249300</v>
       </c>
       <c r="E76" s="3">
+        <v>249900</v>
+      </c>
+      <c r="F76" s="3">
         <v>299900</v>
       </c>
-      <c r="F76" s="3">
-        <v>367900</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>462400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>463400</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>514000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>430600</v>
       </c>
       <c r="L76" s="3">
         <v>430600</v>
       </c>
       <c r="M76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="N76" s="3">
         <v>278800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>276900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3510,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
-      </c>
-      <c r="K80" s="2">
-        <v>44926</v>
       </c>
       <c r="L80" s="2">
         <v>44926</v>
       </c>
       <c r="M80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-27600</v>
+        <v>-15500</v>
       </c>
       <c r="E81" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-43400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>4200</v>
       </c>
       <c r="L81" s="3">
         <v>4200</v>
       </c>
       <c r="M81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="N81" s="3">
         <v>1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,40 +3623,41 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3">
         <v>1800</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3300</v>
+        <v>1200</v>
       </c>
       <c r="E89" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F89" s="3">
         <v>3500</v>
       </c>
-      <c r="F89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
         <v>-5400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13900</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-10900</v>
       </c>
       <c r="L89" s="3">
         <v>-10900</v>
       </c>
       <c r="M89" s="3">
-        <v>-100</v>
+        <v>-10900</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,40 +3949,41 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10100</v>
+        <v>-7000</v>
       </c>
       <c r="E91" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="F91" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-16700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25900</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-21100</v>
       </c>
       <c r="L91" s="3">
         <v>-21100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7600</v>
+        <v>-6500</v>
       </c>
       <c r="E94" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-31200</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>-18200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27800</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-18900</v>
       </c>
       <c r="L94" s="3">
         <v>-18900</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3942,8 +4176,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,49 +4317,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>24800</v>
+        <v>-19100</v>
       </c>
       <c r="E100" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F100" s="3">
         <v>27300</v>
       </c>
-      <c r="F100" s="3">
-        <v>28500</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>24200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>19100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>28400</v>
       </c>
       <c r="L100" s="3">
         <v>28400</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4147,8 +4396,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4156,45 +4405,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E102" s="3">
         <v>13900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-1600</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1300</v>
       </c>
       <c r="L102" s="3">
         <v>-1300</v>
       </c>
       <c r="M102" s="3">
-        <v>-100</v>
+        <v>-1300</v>
       </c>
       <c r="N102" s="3">
         <v>-100</v>
       </c>
       <c r="O102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,121 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
-      </c>
-      <c r="M7" s="2">
-        <v>44926</v>
       </c>
       <c r="N7" s="2">
         <v>44926</v>
       </c>
       <c r="O7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E8" s="3">
         <v>14300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
+      <c r="O8" s="3">
+        <v>100</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
@@ -778,46 +782,49 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E9" s="3">
         <v>8900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6700</v>
       </c>
-      <c r="G9" s="3">
-        <v>5900</v>
-      </c>
       <c r="H9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I9" s="3">
         <v>2100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>3800</v>
       </c>
       <c r="K9" s="3">
         <v>3800</v>
       </c>
       <c r="L9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M9" s="3">
         <v>1900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>100</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -825,46 +832,49 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7500</v>
       </c>
-      <c r="G10" s="3">
-        <v>2600</v>
-      </c>
       <c r="H10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -996,35 +1016,35 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-11500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-7000</v>
       </c>
       <c r="N14" s="3">
         <v>-7000</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1032,41 +1052,44 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E15" s="3">
         <v>3400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-1000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,93 +1121,97 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E17" s="3">
         <v>20600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19700</v>
       </c>
-      <c r="G17" s="3">
-        <v>17300</v>
-      </c>
       <c r="H17" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I17" s="3">
         <v>3400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3900</v>
       </c>
       <c r="N17" s="3">
         <v>3900</v>
       </c>
       <c r="O17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-8800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3800</v>
       </c>
       <c r="N18" s="3">
         <v>-3800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
+      <c r="O18" s="3">
+        <v>-3800</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
@@ -1189,8 +1219,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,46 +1241,47 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-42800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>59300</v>
       </c>
-      <c r="G20" s="3">
-        <v>30300</v>
-      </c>
       <c r="H20" s="3">
+        <v>30500</v>
+      </c>
+      <c r="I20" s="3">
         <v>40300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26900</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5500</v>
       </c>
       <c r="N20" s="3">
         <v>-5500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
+      <c r="O20" s="3">
+        <v>-5500</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
@@ -1255,46 +1289,49 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>40100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-59600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-34700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-38700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23700</v>
-      </c>
-      <c r="M21" s="3">
-        <v>1700</v>
       </c>
       <c r="N21" s="3">
         <v>1700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
+      <c r="O21" s="3">
+        <v>1700</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
@@ -1302,46 +1339,49 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E22" s="3">
         <v>17800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>-200</v>
       </c>
       <c r="N22" s="3">
         <v>-200</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3">
+        <v>-200</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
@@ -1349,93 +1389,99 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E23" s="3">
         <v>18900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-70600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-47800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-43700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>8900</v>
       </c>
       <c r="N23" s="3">
         <v>8900</v>
       </c>
       <c r="O23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
-      </c>
-      <c r="M24" s="3">
-        <v>4700</v>
       </c>
       <c r="N24" s="3">
         <v>4700</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E26" s="3">
         <v>18400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-78200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-43400</v>
       </c>
       <c r="H26" s="3">
         <v>-43400</v>
       </c>
       <c r="I26" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17900</v>
-      </c>
-      <c r="M26" s="3">
-        <v>4200</v>
       </c>
       <c r="N26" s="3">
         <v>4200</v>
       </c>
       <c r="O26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>18400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-78200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-43400</v>
       </c>
       <c r="H27" s="3">
         <v>-43400</v>
       </c>
       <c r="I27" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17900</v>
-      </c>
-      <c r="M27" s="3">
-        <v>4200</v>
       </c>
       <c r="N27" s="3">
         <v>4200</v>
       </c>
       <c r="O27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P27" s="3">
         <v>1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,46 +1839,49 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E32" s="3">
         <v>42800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-59300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-30300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-40300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26900</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5500</v>
       </c>
       <c r="N32" s="3">
         <v>5500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
+      <c r="O32" s="3">
+        <v>5500</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
@@ -1819,55 +1889,61 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>18400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-78200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-43400</v>
       </c>
       <c r="H33" s="3">
         <v>-43400</v>
       </c>
       <c r="I33" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17900</v>
-      </c>
-      <c r="M33" s="3">
-        <v>4200</v>
       </c>
       <c r="N33" s="3">
         <v>4200</v>
       </c>
       <c r="O33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P33" s="3">
         <v>1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>18400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-78200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-43400</v>
       </c>
       <c r="H35" s="3">
         <v>-43400</v>
       </c>
       <c r="I35" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17900</v>
-      </c>
-      <c r="M35" s="3">
-        <v>4200</v>
       </c>
       <c r="N35" s="3">
         <v>4200</v>
       </c>
       <c r="O35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P35" s="3">
         <v>1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
-      </c>
-      <c r="M38" s="2">
-        <v>44926</v>
       </c>
       <c r="N38" s="2">
         <v>44926</v>
       </c>
       <c r="O38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,8 +2136,9 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2076,11 +2163,11 @@
       <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="K41" s="3">
+        <v>100</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -2089,54 +2176,57 @@
         <v>0</v>
       </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>18600</v>
+        <v>14700</v>
       </c>
       <c r="E42" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F42" s="3">
         <v>22900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>28100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>12700</v>
-      </c>
-      <c r="M42" s="3">
-        <v>11000</v>
       </c>
       <c r="N42" s="3">
         <v>11000</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2144,46 +2234,49 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E43" s="3">
         <v>27500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>16700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>13000</v>
       </c>
       <c r="N43" s="3">
         <v>13000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
+      <c r="O43" s="3">
+        <v>13000</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
@@ -2191,46 +2284,49 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>800</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
-      </c>
-      <c r="E44" s="3">
-        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>600</v>
       </c>
       <c r="G44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>500</v>
       </c>
       <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="O44" s="3">
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
@@ -2238,8 +2334,11 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2276,64 +2375,70 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E46" s="3">
         <v>47700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>49500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>36400</v>
-      </c>
-      <c r="M46" s="3">
-        <v>26600</v>
       </c>
       <c r="N46" s="3">
         <v>26600</v>
       </c>
       <c r="O46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="P46" s="3">
         <v>1200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2349,76 +2454,79 @@
       <c r="G47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
         <v>6600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6900</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>9800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>9900</v>
       </c>
       <c r="N47" s="3">
         <v>9900</v>
       </c>
       <c r="O47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P47" s="3">
         <v>295200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>293800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1036900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1010900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>933300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>912600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>946900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1009500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1078400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1043200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>1030000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>865500</v>
       </c>
       <c r="N48" s="3">
         <v>865500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>865500</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -2426,8 +2534,11 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2452,11 +2563,11 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2684,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E52" s="3">
         <v>72100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>66500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>65400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>56400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>67800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>66400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>70000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>61900</v>
       </c>
       <c r="N52" s="3">
         <v>61900</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1154000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1130600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1049400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1049600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1061800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1109700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1191300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1151900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>1146200</v>
-      </c>
-      <c r="M54" s="3">
-        <v>963900</v>
       </c>
       <c r="N54" s="3">
         <v>963900</v>
       </c>
       <c r="O54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="P54" s="3">
         <v>296400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>295200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,46 +2876,47 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E57" s="3">
         <v>30400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>30200</v>
       </c>
       <c r="G57" s="3">
         <v>30200</v>
       </c>
       <c r="H57" s="3">
+        <v>30200</v>
+      </c>
+      <c r="I57" s="3">
         <v>27100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
         <v>8700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>6400</v>
       </c>
       <c r="N57" s="3">
         <v>6400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
+      <c r="O57" s="3">
+        <v>6400</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
@@ -2793,46 +2924,49 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>496600</v>
+      </c>
+      <c r="E58" s="3">
         <v>184700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>170700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>175100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>67200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>415900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>139600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>130300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3">
         <v>215900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>198100</v>
       </c>
       <c r="N58" s="3">
         <v>198100</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2840,140 +2974,149 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E59" s="3">
         <v>4700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>1800</v>
-      </c>
-      <c r="M59" s="3">
-        <v>4000</v>
       </c>
       <c r="N59" s="3">
         <v>4000</v>
       </c>
       <c r="O59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>537300</v>
+      </c>
+      <c r="E60" s="3">
         <v>220000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>200400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>209500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>99300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>444700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>166200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>155400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>226500</v>
-      </c>
-      <c r="M60" s="3">
-        <v>208600</v>
       </c>
       <c r="N60" s="3">
         <v>208600</v>
       </c>
       <c r="O60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E61" s="3">
         <v>396500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>391500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>380400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>456300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>72400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>315100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>290300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>151500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>101200</v>
       </c>
       <c r="N61" s="3">
         <v>101200</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -2981,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2990,46 +3136,49 @@
         <v>4300</v>
       </c>
       <c r="E62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3700</v>
       </c>
       <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>17000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>869100</v>
+      </c>
+      <c r="E66" s="3">
         <v>842000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>800000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>799800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>762000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>741800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>728900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>688500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>632200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>533300</v>
       </c>
       <c r="N66" s="3">
         <v>533300</v>
       </c>
       <c r="O66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="P66" s="3">
         <v>17600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-219200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-201700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-203100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-228900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-160400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-125400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-81500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-69900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-48100</v>
-      </c>
-      <c r="M72" s="3">
-        <v>-63500</v>
       </c>
       <c r="N72" s="3">
         <v>-63500</v>
       </c>
       <c r="O72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="P72" s="3">
         <v>-16400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>284900</v>
+      </c>
+      <c r="E76" s="3">
         <v>288600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>249300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>249900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>299900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>367900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>462400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>463400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>514000</v>
-      </c>
-      <c r="M76" s="3">
-        <v>430600</v>
       </c>
       <c r="N76" s="3">
         <v>430600</v>
       </c>
       <c r="O76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="P76" s="3">
         <v>278800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>276900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
-      </c>
-      <c r="M80" s="2">
-        <v>44926</v>
       </c>
       <c r="N80" s="2">
         <v>44926</v>
       </c>
       <c r="O80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>18400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-78200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-43400</v>
       </c>
       <c r="H81" s="3">
         <v>-43400</v>
       </c>
       <c r="I81" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17900</v>
-      </c>
-      <c r="M81" s="3">
-        <v>4200</v>
       </c>
       <c r="N81" s="3">
         <v>4200</v>
       </c>
       <c r="O81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="P81" s="3">
         <v>1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,29 +4021,30 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -3855,14 +4054,14 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-10900</v>
       </c>
       <c r="N89" s="3">
         <v>-10900</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>-10900</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,46 +4391,47 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-21100</v>
       </c>
       <c r="N91" s="3">
         <v>-21100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27800</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-18900</v>
       </c>
       <c r="N94" s="3">
         <v>-18900</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4416,8 +4650,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>26000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>24200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>19100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>28400</v>
       </c>
       <c r="N100" s="3">
         <v>28400</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4651,8 +4900,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4660,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5200</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-1300</v>
       </c>
       <c r="N102" s="3">
         <v>-1300</v>
       </c>
       <c r="O102" s="3">
-        <v>-100</v>
+        <v>-1300</v>
       </c>
       <c r="P102" s="3">
         <v>-100</v>
       </c>
       <c r="Q102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MRNO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>MRNO</t>
   </si>
@@ -656,128 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
-      </c>
-      <c r="N7" s="2">
-        <v>44926</v>
       </c>
       <c r="O7" s="2">
         <v>44926</v>
       </c>
       <c r="P7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E8" s="3">
         <v>11200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15700</v>
       </c>
-      <c r="G8" s="3">
-        <v>14200</v>
-      </c>
       <c r="H8" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I8" s="3">
         <v>8500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
+      <c r="P8" s="3">
+        <v>100</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
@@ -785,49 +788,52 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7300</v>
       </c>
-      <c r="G9" s="3">
-        <v>6700</v>
-      </c>
       <c r="H9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I9" s="3">
         <v>5700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3800</v>
       </c>
       <c r="L9" s="3">
         <v>3800</v>
       </c>
       <c r="M9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N9" s="3">
         <v>1900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="P9" s="3">
+        <v>100</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -835,49 +841,52 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8400</v>
       </c>
-      <c r="G10" s="3">
-        <v>7500</v>
-      </c>
       <c r="H10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -885,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +917,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,13 +1021,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1019,11 +1038,11 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>-11500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-19000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
@@ -1031,23 +1050,23 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
         <v>5000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-500</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-7000</v>
       </c>
       <c r="O14" s="3">
         <v>-7000</v>
       </c>
       <c r="P14" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1055,44 +1074,47 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
-        <v>5100</v>
-      </c>
       <c r="H15" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-1000</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1105,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,99 +1147,103 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E17" s="3">
         <v>19300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18700</v>
       </c>
-      <c r="G17" s="3">
-        <v>19700</v>
-      </c>
       <c r="H17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I17" s="3">
         <v>17100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3900</v>
       </c>
       <c r="O17" s="3">
         <v>3900</v>
       </c>
       <c r="P17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-5500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-3800</v>
       </c>
       <c r="O18" s="3">
         <v>-3800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
+      <c r="P18" s="3">
+        <v>-3800</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
@@ -1222,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,49 +1274,50 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-42800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
-        <v>59300</v>
-      </c>
       <c r="H20" s="3">
+        <v>62100</v>
+      </c>
+      <c r="I20" s="3">
         <v>30500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>40300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-26900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-5500</v>
       </c>
       <c r="O20" s="3">
         <v>-5500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
+      <c r="P20" s="3">
+        <v>-5500</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
@@ -1292,49 +1325,52 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E21" s="3">
         <v>9700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-59600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-67700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-34700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>23700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>1700</v>
       </c>
       <c r="O21" s="3">
         <v>1700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
+      <c r="P21" s="3">
+        <v>1700</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
@@ -1342,49 +1378,52 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E22" s="3">
         <v>17700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17300</v>
       </c>
-      <c r="G22" s="3">
-        <v>17600</v>
-      </c>
       <c r="H22" s="3">
+        <v>22100</v>
+      </c>
+      <c r="I22" s="3">
         <v>9800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>-200</v>
       </c>
       <c r="O22" s="3">
         <v>-200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
+      <c r="P22" s="3">
+        <v>-200</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
@@ -1392,99 +1431,105 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-70600</v>
-      </c>
       <c r="H23" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-47800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-43700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>8900</v>
       </c>
       <c r="O23" s="3">
         <v>8900</v>
       </c>
       <c r="P23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2000</v>
       </c>
-      <c r="G24" s="3">
-        <v>7600</v>
-      </c>
       <c r="H24" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I24" s="3">
         <v>-4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>4700</v>
       </c>
       <c r="O24" s="3">
         <v>4700</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1492,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-78200</v>
-      </c>
       <c r="H26" s="3">
-        <v>-43400</v>
+        <v>-85300</v>
       </c>
       <c r="I26" s="3">
         <v>-43400</v>
       </c>
       <c r="J26" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>4200</v>
       </c>
       <c r="O26" s="3">
         <v>4200</v>
       </c>
       <c r="P26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-78200</v>
-      </c>
       <c r="H27" s="3">
-        <v>-43400</v>
+        <v>-85300</v>
       </c>
       <c r="I27" s="3">
         <v>-43400</v>
       </c>
       <c r="J27" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-8900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>4200</v>
       </c>
       <c r="O27" s="3">
         <v>4200</v>
       </c>
       <c r="P27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,49 +1908,52 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E32" s="3">
         <v>13900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>42800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-59300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-62100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-30500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-40300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>26900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>5500</v>
       </c>
       <c r="O32" s="3">
         <v>5500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
+      <c r="P32" s="3">
+        <v>5500</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
@@ -1892,58 +1961,64 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-78200</v>
-      </c>
       <c r="H33" s="3">
-        <v>-43400</v>
+        <v>-85300</v>
       </c>
       <c r="I33" s="3">
         <v>-43400</v>
       </c>
       <c r="J33" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>4200</v>
       </c>
       <c r="O33" s="3">
         <v>4200</v>
       </c>
       <c r="P33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-78200</v>
-      </c>
       <c r="H35" s="3">
-        <v>-43400</v>
+        <v>-85300</v>
       </c>
       <c r="I35" s="3">
         <v>-43400</v>
       </c>
       <c r="J35" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>4200</v>
       </c>
       <c r="O35" s="3">
         <v>4200</v>
       </c>
       <c r="P35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
-      </c>
-      <c r="N38" s="2">
-        <v>44926</v>
       </c>
       <c r="O38" s="2">
         <v>44926</v>
       </c>
       <c r="P38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,8 +2222,9 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2166,11 +2252,11 @@
       <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="L41" s="3">
+        <v>100</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -2179,57 +2265,60 @@
         <v>0</v>
       </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
         <v>1000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E42" s="3">
         <v>14700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>12700</v>
-      </c>
-      <c r="N42" s="3">
-        <v>11000</v>
       </c>
       <c r="O42" s="3">
         <v>11000</v>
       </c>
       <c r="P42" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2237,49 +2326,52 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E43" s="3">
         <v>26500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>16700</v>
-      </c>
-      <c r="N43" s="3">
-        <v>13000</v>
       </c>
       <c r="O43" s="3">
         <v>13000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
+      <c r="P43" s="3">
+        <v>13000</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
@@ -2287,49 +2379,52 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
         <v>500</v>
       </c>
       <c r="J44" s="3">
+        <v>500</v>
+      </c>
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
+      <c r="P44" s="3">
+        <v>100</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
@@ -2337,13 +2432,16 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>125700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2378,67 +2476,73 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E46" s="3">
         <v>42900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>47700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>49500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>58500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>36400</v>
-      </c>
-      <c r="N46" s="3">
-        <v>26600</v>
       </c>
       <c r="O46" s="3">
         <v>26600</v>
       </c>
       <c r="P46" s="3">
+        <v>26600</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2457,79 +2561,82 @@
       <c r="H47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>6600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6900</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>9800</v>
-      </c>
-      <c r="N47" s="3">
-        <v>9900</v>
       </c>
       <c r="O47" s="3">
         <v>9900</v>
       </c>
       <c r="P47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="Q47" s="3">
         <v>295200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>293800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>293400</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1036900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1010900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>933300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>912600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>946900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1009500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1078400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1043200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>1030000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>865500</v>
       </c>
       <c r="O48" s="3">
         <v>865500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>865500</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -2537,8 +2644,11 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2566,11 +2676,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2587,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,58 +2803,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E52" s="3">
         <v>74200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>72100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>66500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>65400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>56400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>60600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>67800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>66400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>70000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>61900</v>
       </c>
       <c r="O52" s="3">
         <v>61900</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>61900</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>972100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1154000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1130600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1049400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1049600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1061800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1109700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1191300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1151900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>1146200</v>
-      </c>
-      <c r="N54" s="3">
-        <v>963900</v>
       </c>
       <c r="O54" s="3">
         <v>963900</v>
       </c>
       <c r="P54" s="3">
+        <v>963900</v>
+      </c>
+      <c r="Q54" s="3">
         <v>296400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>295200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,49 +3006,50 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E57" s="3">
         <v>32300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>30200</v>
       </c>
       <c r="H57" s="3">
         <v>30200</v>
       </c>
       <c r="I57" s="3">
+        <v>30200</v>
+      </c>
+      <c r="J57" s="3">
         <v>27100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>8700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>6400</v>
       </c>
       <c r="O57" s="3">
         <v>6400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="P57" s="3">
+        <v>6400</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -2927,49 +3057,52 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>610800</v>
+      </c>
+      <c r="E58" s="3">
         <v>496600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>184700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>170700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>175100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>67200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>415900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>139600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>130300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N58" s="3">
         <v>215900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>198100</v>
       </c>
       <c r="O58" s="3">
         <v>198100</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>198100</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -2977,149 +3110,158 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>1800</v>
-      </c>
-      <c r="N59" s="3">
-        <v>4000</v>
       </c>
       <c r="O59" s="3">
         <v>4000</v>
       </c>
       <c r="P59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>662600</v>
+      </c>
+      <c r="E60" s="3">
         <v>537300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>220000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>200400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>209500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>99300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>444700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>166200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>155400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>226500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>208600</v>
       </c>
       <c r="O60" s="3">
         <v>208600</v>
       </c>
       <c r="P60" s="3">
+        <v>208600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E61" s="3">
         <v>99600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>396500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>391500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>380400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>456300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>72400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>315100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>290300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>151500</v>
-      </c>
-      <c r="N61" s="3">
-        <v>101200</v>
       </c>
       <c r="O61" s="3">
         <v>101200</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>101200</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3127,58 +3269,64 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4300</v>
+        <v>5000</v>
       </c>
       <c r="E62" s="3">
         <v>4300</v>
       </c>
       <c r="F62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3700</v>
       </c>
       <c r="K62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="L62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>17000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>844000</v>
+      </c>
+      <c r="E66" s="3">
         <v>869100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>842000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>800000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>799800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>762000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>741800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>728900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>688500</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>632200</v>
-      </c>
-      <c r="N66" s="3">
-        <v>533300</v>
       </c>
       <c r="O66" s="3">
         <v>533300</v>
       </c>
       <c r="P66" s="3">
+        <v>533300</v>
+      </c>
+      <c r="Q66" s="3">
         <v>17600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-280600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-219200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-201700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-203100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-228900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-160400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-125400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-81500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-69900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-48100</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-63500</v>
       </c>
       <c r="O72" s="3">
         <v>-63500</v>
       </c>
       <c r="P72" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-16800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E76" s="3">
         <v>284900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>288600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>249300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>249900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>299900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>367900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>462400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>463400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>514000</v>
-      </c>
-      <c r="N76" s="3">
-        <v>430600</v>
       </c>
       <c r="O76" s="3">
         <v>430600</v>
       </c>
       <c r="P76" s="3">
+        <v>430600</v>
+      </c>
+      <c r="Q76" s="3">
         <v>278800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>276900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>274000</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
-      </c>
-      <c r="N80" s="2">
-        <v>44926</v>
       </c>
       <c r="O80" s="2">
         <v>44926</v>
       </c>
       <c r="P80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-78200</v>
-      </c>
       <c r="H81" s="3">
-        <v>-43400</v>
+        <v>-85300</v>
       </c>
       <c r="I81" s="3">
         <v>-43400</v>
       </c>
       <c r="J81" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>4200</v>
       </c>
       <c r="O81" s="3">
         <v>4200</v>
       </c>
       <c r="P81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,32 +4219,33 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -4057,14 +4255,14 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4072,8 +4270,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4400</v>
-      </c>
       <c r="H89" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I89" s="3">
         <v>3500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13900</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-10900</v>
       </c>
       <c r="O89" s="3">
         <v>-10900</v>
       </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>-10900</v>
       </c>
       <c r="Q89" s="3">
         <v>-100</v>
       </c>
       <c r="R89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,49 +4611,50 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-10200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-7800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-31200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25900</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-21100</v>
       </c>
       <c r="O91" s="3">
         <v>-21100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-21100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4442,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6500</v>
       </c>
-      <c r="G94" s="3">
-        <v>-7700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-18900</v>
       </c>
       <c r="O94" s="3">
         <v>-18900</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>-18900</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-293300</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4653,8 +4886,8 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5054,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19100</v>
       </c>
-      <c r="G100" s="3">
-        <v>26000</v>
-      </c>
       <c r="H100" s="3">
+        <v>45200</v>
+      </c>
+      <c r="I100" s="3">
         <v>27300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>39400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>19100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>28400</v>
       </c>
       <c r="O100" s="3">
         <v>28400</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4903,8 +5151,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -4912,54 +5160,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24400</v>
       </c>
-      <c r="G102" s="3">
-        <v>13900</v>
-      </c>
       <c r="H102" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I102" s="3">
         <v>28300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5200</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-1300</v>
       </c>
       <c r="O102" s="3">
         <v>-1300</v>
       </c>
       <c r="P102" s="3">
-        <v>-100</v>
+        <v>-1300</v>
       </c>
       <c r="Q102" s="3">
         <v>-100</v>
       </c>
       <c r="R102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
     </row>
